--- a/guides/MTPE_윈도우_설치운영_가이드.xlsx
+++ b/guides/MTPE_윈도우_설치운영_가이드.xlsx
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>B-2</t>
@@ -858,19 +858,19 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>릴리스 페이지 열기</t>
+          <t>릴리스 목록 열기</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
           <t>주소창에 아래를 입력해 엽니다:
-https://github.com/youngjoochoi-maker/mtpe-translator/releases/latest
+https://github.com/youngjoochoi-maker/mtpe-translator/releases
 (권한이 없으면 'Not Found'가 떠요 → 운영자에게 '저장소에 초대(collaborator)해 주세요' 요청)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>최신 버전(Release) 화면이 보임</t>
+          <t>여러 버전(Releases) 목록이 보임</t>
         </is>
       </c>
     </row>
@@ -882,22 +882,44 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
+          <t>MTPE 최신 버전 고르기</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>목록에서 이름이 v1.1.1 처럼 v로 시작하는 것 중 가장 위(최신)를 클릭. ※ splitter-… / api-… 로 시작하는 건 다른 프로그램이니 무시하세요.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>MTPE.exe 가 첨부된 버전 화면이 열림</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>B-4</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
           <t>MTPE.exe 내려받기</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>화면 아래쪽 'Assets' 목록에서 MTPE.exe 를 클릭하면 다운로드됩니다.</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>그 화면 아래 'Assets' 목록에서 MTPE.exe 를 클릭하면 다운로드됩니다.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>다운로드 폴더에 MTPE.exe (약 58MB)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>※ 비개발자라면 방법 A(운영자에게 파일 받기)가 제일 쉽습니다. 운영자 한 명이 방법 B로 한 번 받아두고, 그 MTPE.exe를 사내에 공유하면 나머지 분들은 받기만 하면 됩니다. ※ 프로그램이 업데이트되면 새 MTPE.exe로 같은 방식으로 교체하면 됩니다.</t>
         </is>
@@ -905,7 +927,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
